--- a/docs/sample-preserve.xlsx
+++ b/docs/sample-preserve.xlsx
@@ -109,10 +109,10 @@
       <c r="A6" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="n" s="0">
+      <c r="B6" t="n">
         <v>85000.0</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="C6" t="s">
         <v>4</v>
       </c>
     </row>
@@ -120,10 +120,10 @@
       <c r="A7" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="n" s="0">
+      <c r="B7" t="n">
         <v>75000.0</v>
       </c>
-      <c r="C7" t="s" s="0">
+      <c r="C7" t="s">
         <v>7</v>
       </c>
     </row>

--- a/docs/sample-preserve.xlsx
+++ b/docs/sample-preserve.xlsx
@@ -109,10 +109,10 @@
       <c r="A6" t="s" s="0">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="n" s="0">
         <v>85000.0</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" t="s" s="0">
         <v>4</v>
       </c>
     </row>
@@ -120,10 +120,10 @@
       <c r="A7" t="s" s="0">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="n" s="0">
         <v>75000.0</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" t="s" s="0">
         <v>7</v>
       </c>
     </row>

--- a/docs/sample-preserve.xlsx
+++ b/docs/sample-preserve.xlsx
@@ -32,10 +32,10 @@
     <t>Bob</t>
   </si>
   <si>
-    <t>Carol</t>
+    <t>Sales</t>
   </si>
   <si>
-    <t>Sales</t>
+    <t>Carol</t>
   </si>
 </sst>
 </file>
@@ -118,13 +118,13 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="0">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" t="n">
         <v>75000.0</v>
       </c>
       <c r="C7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
